--- a/MDC/MDC_Contenido_t.xlsx
+++ b/MDC/MDC_Contenido_t.xlsx
@@ -1297,7 +1297,7 @@
     <t>06410211.01</t>
   </si>
   <si>
-    <t>Yip's</t>
+    <t>Supermercado 1</t>
   </si>
   <si>
     <t>Contenido</t>
@@ -1513,7 +1513,7 @@
     <t>9</t>
   </si>
   <si>
-    <t>La Colonia # 1</t>
+    <t>Supermercado 2</t>
   </si>
   <si>
     <t>Pronto</t>
@@ -1528,7 +1528,7 @@
     <t>Foodmart</t>
   </si>
   <si>
-    <t>Los almendros</t>
+    <t>Mercadito 1</t>
   </si>
   <si>
     <t>Mercadito Precio t</t>
@@ -1549,7 +1549,7 @@
     <t>55</t>
   </si>
   <si>
-    <t>5 estrellas</t>
+    <t>Mercadito 2</t>
   </si>
   <si>
     <t>Escuela 1</t>
